--- a/rl3.xlsx
+++ b/rl3.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Лист 1" sheetId="19" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" calcMode="autoNoTable" iterateCount="1000" iterateDelta="9.9999999999999995E-8"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -84,9 +84,6 @@
     <t>transpor + truckNumber</t>
   </si>
   <si>
-    <t>transportCompany</t>
-  </si>
-  <si>
     <t>MR №</t>
   </si>
   <si>
@@ -103,6 +100,9 @@
   </si>
   <si>
     <t>specialist</t>
+  </si>
+  <si>
+    <t>Общество с ограниченной ответственностью "УСПЕХ", 121596, Москва г, Горбунова ул, дом № 2, строение 3, помещение II, комната 12</t>
   </si>
 </sst>
 </file>
@@ -112,7 +112,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -173,6 +173,23 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -578,10 +595,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -896,7 +913,7 @@
     </row>
     <row r="2" spans="1:13" s="3" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="45" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="45"/>
       <c r="C2" s="45"/>
@@ -957,7 +974,7 @@
       </c>
       <c r="F6" s="51"/>
       <c r="G6" s="52" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H6" s="53"/>
       <c r="M6" s="1"/>
@@ -977,7 +994,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8" s="43"/>
       <c r="D8" s="43"/>
@@ -1031,10 +1048,10 @@
       <c r="E12" s="22"/>
       <c r="F12" s="23"/>
       <c r="G12" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="25" t="s">
         <v>26</v>
-      </c>
-      <c r="H12" s="25" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:13" s="3" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1047,7 +1064,7 @@
       <c r="C13" s="24"/>
       <c r="D13" s="27"/>
       <c r="E13" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="24"/>
@@ -1064,7 +1081,7 @@
       <c r="C14" s="29"/>
       <c r="D14" s="30"/>
       <c r="E14" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F14" s="16"/>
       <c r="G14" s="31"/>
@@ -1081,7 +1098,7 @@
       <c r="C15" s="29"/>
       <c r="D15" s="30"/>
       <c r="E15" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F15" s="16"/>
       <c r="G15" s="31"/>
@@ -1098,7 +1115,7 @@
       <c r="C16" s="29"/>
       <c r="D16" s="30"/>
       <c r="E16" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F16" s="16"/>
       <c r="G16" s="31"/>
@@ -1115,7 +1132,7 @@
       <c r="C17" s="29"/>
       <c r="D17" s="30"/>
       <c r="E17" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F17" s="16"/>
       <c r="G17" s="31"/>
@@ -1132,7 +1149,7 @@
       <c r="C18" s="30"/>
       <c r="D18" s="30"/>
       <c r="E18" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F18" s="18"/>
       <c r="G18" s="21"/>
@@ -1141,7 +1158,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B19" s="33"/>
       <c r="C19" s="33"/>
